--- a/Design/config/ForceConfig.xlsx
+++ b/Design/config/ForceConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$D$5</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -174,6 +174,22 @@
   </si>
   <si>
     <t>在野</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>难度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -571,16 +587,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="9.5" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="7.5" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,13 +605,16 @@
         <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -602,13 +622,16 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -616,13 +639,16 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -630,13 +656,16 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -644,13 +673,16 @@
         <v>10</v>
       </c>
       <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
         <v>100001</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -658,13 +690,16 @@
         <v>12</v>
       </c>
       <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
         <v>100002</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -672,13 +707,16 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4">
         <v>100003</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -686,13 +724,16 @@
         <v>18</v>
       </c>
       <c r="C8" s="4">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4">
         <v>100004</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -700,13 +741,16 @@
         <v>17</v>
       </c>
       <c r="C9" s="4">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4">
         <v>100005</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -714,13 +758,16 @@
         <v>21</v>
       </c>
       <c r="C10" s="4">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4">
         <v>100006</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -728,13 +775,16 @@
         <v>24</v>
       </c>
       <c r="C11" s="4">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4">
         <v>100007</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -742,13 +792,16 @@
         <v>25</v>
       </c>
       <c r="C12" s="4">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4">
         <v>100008</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -756,13 +809,16 @@
         <v>23</v>
       </c>
       <c r="C13" s="4">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4">
         <v>100009</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -770,13 +826,16 @@
         <v>33</v>
       </c>
       <c r="C14" s="4">
+        <v>4</v>
+      </c>
+      <c r="D14" s="4">
         <v>100010</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -784,13 +843,16 @@
         <v>35</v>
       </c>
       <c r="C15" s="4">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4">
         <v>100011</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>12</v>
       </c>
@@ -798,13 +860,16 @@
         <v>37</v>
       </c>
       <c r="C16" s="4">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4">
         <v>100012</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>99</v>
       </c>
@@ -812,14 +877,17 @@
         <v>40</v>
       </c>
       <c r="C17" s="4">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4">
         <v>100020</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C5">
+  <autoFilter ref="A4:D5">
     <sortState ref="A5:C9">
       <sortCondition ref="A4:A5"/>
     </sortState>

--- a/Design/config/ForceConfig.xlsx
+++ b/Design/config/ForceConfig.xlsx
@@ -169,10 +169,6 @@
     <t>#A385AD</t>
   </si>
   <si>
-    <t>#CCCCCC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>在野</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -190,6 +186,10 @@
   </si>
   <si>
     <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#666666</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -605,7 +605,7 @@
         <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>16</v>
@@ -622,7 +622,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>15</v>
@@ -639,7 +639,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -656,7 +656,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
@@ -874,7 +874,7 @@
         <v>99</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="4">
         <v>0</v>
@@ -883,7 +883,7 @@
         <v>100020</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/ForceConfig.xlsx
+++ b/Design/config/ForceConfig.xlsx
@@ -74,10 +74,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>孙权</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -190,6 +186,10 @@
   </si>
   <si>
     <t>#666666</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>孙策</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -605,10 +605,10 @@
         <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>11</v>
@@ -622,13 +622,13 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -639,10 +639,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>3</v>
@@ -656,7 +656,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
@@ -679,7 +679,7 @@
         <v>100001</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -696,7 +696,7 @@
         <v>100002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -704,7 +704,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C7" s="4">
         <v>2</v>
@@ -713,7 +713,7 @@
         <v>100003</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -721,7 +721,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4">
         <v>3</v>
@@ -730,7 +730,7 @@
         <v>100004</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -738,7 +738,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="4">
         <v>3</v>
@@ -747,7 +747,7 @@
         <v>100005</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -755,7 +755,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="4">
         <v>4</v>
@@ -764,7 +764,7 @@
         <v>100006</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -772,7 +772,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="4">
         <v>3</v>
@@ -781,7 +781,7 @@
         <v>100007</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -789,7 +789,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="4">
         <v>3</v>
@@ -798,7 +798,7 @@
         <v>100008</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -806,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4">
         <v>5</v>
@@ -815,7 +815,7 @@
         <v>100009</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -823,7 +823,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="4">
         <v>4</v>
@@ -832,7 +832,7 @@
         <v>100010</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -840,7 +840,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4">
         <v>5</v>
@@ -849,7 +849,7 @@
         <v>100011</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -857,7 +857,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="4">
         <v>5</v>
@@ -866,7 +866,7 @@
         <v>100012</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -874,7 +874,7 @@
         <v>99</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="4">
         <v>0</v>
@@ -883,7 +883,7 @@
         <v>100020</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/ForceConfig.xlsx
+++ b/Design/config/ForceConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -190,6 +190,30 @@
   </si>
   <si>
     <t>孙策</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始金钱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始粮食</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitGold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitFood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -587,17 +611,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.75" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
     <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="4" width="9.5" customWidth="1"/>
-    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,10 +635,16 @@
         <v>15</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -628,10 +658,16 @@
         <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -645,10 +681,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -662,10 +704,16 @@
         <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -678,11 +726,17 @@
       <c r="D5" s="4">
         <v>100001</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="4">
+        <v>200</v>
+      </c>
+      <c r="F5" s="4">
+        <v>200</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -695,11 +749,17 @@
       <c r="D6" s="4">
         <v>100002</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="4">
+        <v>200</v>
+      </c>
+      <c r="F6" s="4">
+        <v>200</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -712,11 +772,17 @@
       <c r="D7" s="4">
         <v>100003</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="4">
+        <v>200</v>
+      </c>
+      <c r="F7" s="4">
+        <v>200</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -729,11 +795,17 @@
       <c r="D8" s="4">
         <v>100004</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4">
+        <v>200</v>
+      </c>
+      <c r="F8" s="4">
+        <v>200</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -746,11 +818,17 @@
       <c r="D9" s="4">
         <v>100005</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4">
+        <v>200</v>
+      </c>
+      <c r="F9" s="4">
+        <v>200</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -763,11 +841,17 @@
       <c r="D10" s="4">
         <v>100006</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4">
+        <v>200</v>
+      </c>
+      <c r="F10" s="4">
+        <v>200</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -780,11 +864,17 @@
       <c r="D11" s="4">
         <v>100007</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4">
+        <v>200</v>
+      </c>
+      <c r="F11" s="4">
+        <v>200</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -797,11 +887,17 @@
       <c r="D12" s="4">
         <v>100008</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4">
+        <v>200</v>
+      </c>
+      <c r="F12" s="4">
+        <v>200</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -814,11 +910,17 @@
       <c r="D13" s="4">
         <v>100009</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4">
+        <v>200</v>
+      </c>
+      <c r="F13" s="4">
+        <v>200</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -831,11 +933,17 @@
       <c r="D14" s="4">
         <v>100010</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4">
+        <v>200</v>
+      </c>
+      <c r="F14" s="4">
+        <v>200</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -848,11 +956,17 @@
       <c r="D15" s="4">
         <v>100011</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4">
+        <v>200</v>
+      </c>
+      <c r="F15" s="4">
+        <v>200</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>12</v>
       </c>
@@ -865,11 +979,17 @@
       <c r="D16" s="4">
         <v>100012</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4">
+        <v>200</v>
+      </c>
+      <c r="F16" s="4">
+        <v>200</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>99</v>
       </c>
@@ -882,7 +1002,13 @@
       <c r="D17" s="4">
         <v>100020</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4">
+        <v>200</v>
+      </c>
+      <c r="F17" s="4">
+        <v>200</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>43</v>
       </c>
     </row>

--- a/Design/config/ForceConfig.xlsx
+++ b/Design/config/ForceConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -197,23 +197,39 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>初始粮食</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>InitGold</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>InitFood</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitWood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitHorse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitSteel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始木</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -611,17 +627,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.75" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
     <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="9.5" customWidth="1"/>
+    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,13 +654,19 @@
         <v>45</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -658,16 +680,22 @@
         <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -681,16 +709,22 @@
         <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -704,16 +738,22 @@
         <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -730,13 +770,19 @@
         <v>200</v>
       </c>
       <c r="F5" s="4">
-        <v>200</v>
-      </c>
-      <c r="G5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4">
+        <v>10</v>
+      </c>
+      <c r="H5" s="4">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -753,13 +799,19 @@
         <v>200</v>
       </c>
       <c r="F6" s="4">
-        <v>200</v>
-      </c>
-      <c r="G6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4">
+        <v>10</v>
+      </c>
+      <c r="H6" s="4">
+        <v>10</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -776,13 +828,19 @@
         <v>200</v>
       </c>
       <c r="F7" s="4">
-        <v>200</v>
-      </c>
-      <c r="G7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4">
+        <v>10</v>
+      </c>
+      <c r="H7" s="4">
+        <v>10</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -799,13 +857,19 @@
         <v>200</v>
       </c>
       <c r="F8" s="4">
-        <v>200</v>
-      </c>
-      <c r="G8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4">
+        <v>10</v>
+      </c>
+      <c r="H8" s="4">
+        <v>10</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -822,13 +886,19 @@
         <v>200</v>
       </c>
       <c r="F9" s="4">
-        <v>200</v>
-      </c>
-      <c r="G9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4">
+        <v>10</v>
+      </c>
+      <c r="H9" s="4">
+        <v>10</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -845,13 +915,19 @@
         <v>200</v>
       </c>
       <c r="F10" s="4">
-        <v>200</v>
-      </c>
-      <c r="G10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="4">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4">
+        <v>10</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -868,13 +944,19 @@
         <v>200</v>
       </c>
       <c r="F11" s="4">
-        <v>200</v>
-      </c>
-      <c r="G11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="4">
+        <v>10</v>
+      </c>
+      <c r="H11" s="4">
+        <v>10</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -891,13 +973,19 @@
         <v>200</v>
       </c>
       <c r="F12" s="4">
-        <v>200</v>
-      </c>
-      <c r="G12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="4">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4">
+        <v>10</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -914,13 +1002,19 @@
         <v>200</v>
       </c>
       <c r="F13" s="4">
-        <v>200</v>
-      </c>
-      <c r="G13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4">
+        <v>10</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -937,13 +1031,19 @@
         <v>200</v>
       </c>
       <c r="F14" s="4">
-        <v>200</v>
-      </c>
-      <c r="G14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="4">
+        <v>10</v>
+      </c>
+      <c r="H14" s="4">
+        <v>10</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -960,13 +1060,19 @@
         <v>200</v>
       </c>
       <c r="F15" s="4">
-        <v>200</v>
-      </c>
-      <c r="G15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="4">
+        <v>10</v>
+      </c>
+      <c r="H15" s="4">
+        <v>10</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>12</v>
       </c>
@@ -983,13 +1089,19 @@
         <v>200</v>
       </c>
       <c r="F16" s="4">
-        <v>200</v>
-      </c>
-      <c r="G16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="4">
+        <v>10</v>
+      </c>
+      <c r="H16" s="4">
+        <v>10</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>99</v>
       </c>
@@ -1006,9 +1118,15 @@
         <v>200</v>
       </c>
       <c r="F17" s="4">
-        <v>200</v>
-      </c>
-      <c r="G17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="4">
+        <v>10</v>
+      </c>
+      <c r="H17" s="4">
+        <v>10</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>43</v>
       </c>
     </row>

--- a/Design/config/ForceConfig.xlsx
+++ b/Design/config/ForceConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -230,6 +230,14 @@
   </si>
   <si>
     <t>铁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitStone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>石头</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -627,17 +635,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.75" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
     <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="8" width="9.5" customWidth="1"/>
-    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="9.5" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,10 +671,13 @@
         <v>54</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -692,10 +703,13 @@
         <v>51</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -721,10 +735,13 @@
         <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -752,8 +769,11 @@
       <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -778,11 +798,14 @@
       <c r="H5" s="4">
         <v>10</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="4">
+        <v>10</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -807,11 +830,14 @@
       <c r="H6" s="4">
         <v>10</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="4">
+        <v>10</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -836,11 +862,14 @@
       <c r="H7" s="4">
         <v>10</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="4">
+        <v>10</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -865,11 +894,14 @@
       <c r="H8" s="4">
         <v>10</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4">
+        <v>10</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -894,11 +926,14 @@
       <c r="H9" s="4">
         <v>10</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4">
+        <v>10</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -923,11 +958,14 @@
       <c r="H10" s="4">
         <v>10</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4">
+        <v>10</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -952,11 +990,14 @@
       <c r="H11" s="4">
         <v>10</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4">
+        <v>10</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -981,11 +1022,14 @@
       <c r="H12" s="4">
         <v>10</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4">
+        <v>10</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -1010,11 +1054,14 @@
       <c r="H13" s="4">
         <v>10</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4">
+        <v>10</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -1039,11 +1086,14 @@
       <c r="H14" s="4">
         <v>10</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4">
+        <v>10</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -1068,11 +1118,14 @@
       <c r="H15" s="4">
         <v>10</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4">
+        <v>10</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>12</v>
       </c>
@@ -1097,11 +1150,14 @@
       <c r="H16" s="4">
         <v>10</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4">
+        <v>10</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>99</v>
       </c>
@@ -1126,7 +1182,10 @@
       <c r="H17" s="4">
         <v>10</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="4">
+        <v>10</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>43</v>
       </c>
     </row>

--- a/Design/config/ForceConfig.xlsx
+++ b/Design/config/ForceConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -206,38 +206,6 @@
   </si>
   <si>
     <t>cs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>InitWood</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>InitHorse</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>InitSteel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始木</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>马</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>InitStone</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>石头</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -635,17 +603,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.75" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
     <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.5" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -662,22 +630,10 @@
         <v>45</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -694,22 +650,10 @@
         <v>46</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -726,22 +670,10 @@
         <v>47</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -758,22 +690,10 @@
         <v>48</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -789,23 +709,11 @@
       <c r="E5" s="4">
         <v>200</v>
       </c>
-      <c r="F5" s="4">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4">
-        <v>10</v>
-      </c>
-      <c r="H5" s="4">
-        <v>10</v>
-      </c>
-      <c r="I5" s="4">
-        <v>10</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -821,23 +729,11 @@
       <c r="E6" s="4">
         <v>200</v>
       </c>
-      <c r="F6" s="4">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4">
-        <v>10</v>
-      </c>
-      <c r="H6" s="4">
-        <v>10</v>
-      </c>
-      <c r="I6" s="4">
-        <v>10</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -853,23 +749,11 @@
       <c r="E7" s="4">
         <v>200</v>
       </c>
-      <c r="F7" s="4">
-        <v>10</v>
-      </c>
-      <c r="G7" s="4">
-        <v>10</v>
-      </c>
-      <c r="H7" s="4">
-        <v>10</v>
-      </c>
-      <c r="I7" s="4">
-        <v>10</v>
-      </c>
-      <c r="J7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -885,23 +769,11 @@
       <c r="E8" s="4">
         <v>200</v>
       </c>
-      <c r="F8" s="4">
-        <v>10</v>
-      </c>
-      <c r="G8" s="4">
-        <v>10</v>
-      </c>
-      <c r="H8" s="4">
-        <v>10</v>
-      </c>
-      <c r="I8" s="4">
-        <v>10</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -917,23 +789,11 @@
       <c r="E9" s="4">
         <v>200</v>
       </c>
-      <c r="F9" s="4">
-        <v>10</v>
-      </c>
-      <c r="G9" s="4">
-        <v>10</v>
-      </c>
-      <c r="H9" s="4">
-        <v>10</v>
-      </c>
-      <c r="I9" s="4">
-        <v>10</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -949,23 +809,11 @@
       <c r="E10" s="4">
         <v>200</v>
       </c>
-      <c r="F10" s="4">
-        <v>10</v>
-      </c>
-      <c r="G10" s="4">
-        <v>10</v>
-      </c>
-      <c r="H10" s="4">
-        <v>10</v>
-      </c>
-      <c r="I10" s="4">
-        <v>10</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -981,23 +829,11 @@
       <c r="E11" s="4">
         <v>200</v>
       </c>
-      <c r="F11" s="4">
-        <v>10</v>
-      </c>
-      <c r="G11" s="4">
-        <v>10</v>
-      </c>
-      <c r="H11" s="4">
-        <v>10</v>
-      </c>
-      <c r="I11" s="4">
-        <v>10</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -1013,23 +849,11 @@
       <c r="E12" s="4">
         <v>200</v>
       </c>
-      <c r="F12" s="4">
-        <v>10</v>
-      </c>
-      <c r="G12" s="4">
-        <v>10</v>
-      </c>
-      <c r="H12" s="4">
-        <v>10</v>
-      </c>
-      <c r="I12" s="4">
-        <v>10</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -1045,23 +869,11 @@
       <c r="E13" s="4">
         <v>200</v>
       </c>
-      <c r="F13" s="4">
-        <v>10</v>
-      </c>
-      <c r="G13" s="4">
-        <v>10</v>
-      </c>
-      <c r="H13" s="4">
-        <v>10</v>
-      </c>
-      <c r="I13" s="4">
-        <v>10</v>
-      </c>
-      <c r="J13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -1077,23 +889,11 @@
       <c r="E14" s="4">
         <v>200</v>
       </c>
-      <c r="F14" s="4">
-        <v>10</v>
-      </c>
-      <c r="G14" s="4">
-        <v>10</v>
-      </c>
-      <c r="H14" s="4">
-        <v>10</v>
-      </c>
-      <c r="I14" s="4">
-        <v>10</v>
-      </c>
-      <c r="J14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -1109,23 +909,11 @@
       <c r="E15" s="4">
         <v>200</v>
       </c>
-      <c r="F15" s="4">
-        <v>10</v>
-      </c>
-      <c r="G15" s="4">
-        <v>10</v>
-      </c>
-      <c r="H15" s="4">
-        <v>10</v>
-      </c>
-      <c r="I15" s="4">
-        <v>10</v>
-      </c>
-      <c r="J15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>12</v>
       </c>
@@ -1141,23 +929,11 @@
       <c r="E16" s="4">
         <v>200</v>
       </c>
-      <c r="F16" s="4">
-        <v>10</v>
-      </c>
-      <c r="G16" s="4">
-        <v>10</v>
-      </c>
-      <c r="H16" s="4">
-        <v>10</v>
-      </c>
-      <c r="I16" s="4">
-        <v>10</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>99</v>
       </c>
@@ -1173,19 +949,7 @@
       <c r="E17" s="4">
         <v>200</v>
       </c>
-      <c r="F17" s="4">
-        <v>10</v>
-      </c>
-      <c r="G17" s="4">
-        <v>10</v>
-      </c>
-      <c r="H17" s="4">
-        <v>10</v>
-      </c>
-      <c r="I17" s="4">
-        <v>10</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>43</v>
       </c>
     </row>
